--- a/face recognition/reports/attendance_2026-10-14.xlsx
+++ b/face recognition/reports/attendance_2026-10-14.xlsx
@@ -1003,7 +1003,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>17 ساعت و 5 دقیقه (تا الان)</t>
+          <t>19 ساعت و 42 دقیقه (تا الان)</t>
         </is>
       </c>
       <c r="I4" s="7" t="n">
